--- a/results/failedExecutionList.xlsx
+++ b/results/failedExecutionList.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12495"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3180" uniqueCount="170">
   <si>
     <t>TestName</t>
   </si>
@@ -34,13 +47,10 @@
     <t>uat</t>
   </si>
   <si>
-    <t>WEB-Produkti-Prikaz_produktov-Kredit</t>
-  </si>
-  <si>
-    <t>C65817</t>
-  </si>
-  <si>
-    <t>5,</t>
+    <t>Products_Current_Accounts-Cheques_[WEB]</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>data</t>
@@ -52,843 +62,492 @@
     <t>off</t>
   </si>
   <si>
-    <t>C57853</t>
-  </si>
-  <si>
-    <t>PLA-242_WebLogin_1_(Positive_Scenario)</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>PLA-242_WebLogin_2_(Click_outside_username)</t>
-  </si>
-  <si>
-    <t>C63631</t>
-  </si>
-  <si>
-    <t>4,</t>
-  </si>
-  <si>
-    <t>WEB_Sporocanje_Novo_sporocilo</t>
-  </si>
-  <si>
-    <t>C63328</t>
-  </si>
-  <si>
-    <t>PLA_WEB-PFM-Insights_page+Product_selector</t>
-  </si>
-  <si>
-    <t>C59031</t>
-  </si>
-  <si>
-    <t>PLA_616_WEB-Placila-Interni_prenos:VR-OR_EUR#1</t>
-  </si>
-  <si>
-    <t>C59942</t>
+    <t>Payments-Payments_Overview_[WEB]</t>
+  </si>
+  <si>
+    <t>C70799</t>
   </si>
   <si>
     <t>3,</t>
   </si>
   <si>
-    <t>WEB-Kontakti-Novo_placilo</t>
-  </si>
-  <si>
-    <t>C57612</t>
-  </si>
-  <si>
-    <t>WEB-Vstopna_stran-Menu</t>
-  </si>
-  <si>
-    <t>C57727</t>
-  </si>
-  <si>
-    <t>WEB-Vstopna_stran-Pozabljeno_geslo</t>
-  </si>
-  <si>
-    <t>C57730</t>
-  </si>
-  <si>
-    <t>WEB-Osebni_racun-Transakcije-Grupiranje</t>
-  </si>
-  <si>
-    <t>C57027</t>
-  </si>
-  <si>
-    <t>WEB-Varcevalni_racun-Transakcije-Grupiranje</t>
-  </si>
-  <si>
-    <t>C57041</t>
-  </si>
-  <si>
-    <t>2,</t>
-  </si>
-  <si>
-    <t>WEB-Varcevalni_racun-Transakcije-Izvoz</t>
-  </si>
-  <si>
-    <t>C57045</t>
-  </si>
-  <si>
-    <t>WEB-Varcevanje-Grupiranje</t>
-  </si>
-  <si>
-    <t>C57079</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Vpis_in_registracija-Izpis_uporabnika</t>
-  </si>
-  <si>
-    <t>C57171</t>
-  </si>
-  <si>
-    <t>PLA-502_WEB_Sporocanje_Novo_sporocilo_Vprasanje</t>
-  </si>
-  <si>
-    <t>C63344</t>
-  </si>
-  <si>
-    <t>PLA-655_WEB_Sporocanje_Novo_sporocilo_Tehnicna_pomoc</t>
-  </si>
-  <si>
-    <t>C63347</t>
-  </si>
-  <si>
-    <t>PLA-656_WEB_Sporocanje_Novo_sporocilo_Vprasanje_s_priponko</t>
-  </si>
-  <si>
-    <t>C63348</t>
-  </si>
-  <si>
-    <t>PLA-657_WEB_Sporocanje_Novo_sporocilo_Pritozba_s_priponko</t>
-  </si>
-  <si>
-    <t>C63349</t>
-  </si>
-  <si>
-    <t>PLA-659_WEB_Sporocanje_Novo_sporocilo_Tehnicna_pomoc_s_priponko</t>
-  </si>
-  <si>
-    <t>C63351</t>
-  </si>
-  <si>
-    <t>WEB-Sporocanje-Seznam_Podrobnosti_pritozb/ugovora_2</t>
-  </si>
-  <si>
-    <t>C58072,C58073</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_EUR-Gumb_Preklici_1</t>
-  </si>
-  <si>
-    <t>C57154</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_EUR-Gumb_Preklici_2</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_EUR-Gumb_Preklici_3</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_EUR-Gumb_nazaj_1</t>
-  </si>
-  <si>
-    <t>C57155</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_tuji_valuti-Gumb_Preklici_1</t>
-  </si>
-  <si>
-    <t>C57160</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_tuji_valuti-Gumb_Preklici_2</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_tuji_valuti-Gumb_Preklici_3</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_tuji_valuti-Gumb_nazaj_1</t>
-  </si>
-  <si>
-    <t>C57161</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Gumb_Preklici_1</t>
-  </si>
-  <si>
-    <t>C57168</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Gumb_Preklici_2</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Gumb_Preklici_3</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Izven_EGP-Gumb_Preklici_1</t>
-  </si>
-  <si>
-    <t>C58046</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Izven_EGP-Gumb_Preklici_2</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Izven_EGP-Gumb_Preklici_3</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Izven_EGP-Gumb_nazaj_2</t>
-  </si>
-  <si>
-    <t>C58047</t>
-  </si>
-  <si>
-    <t>WEB-Cezmejno_placilo-Gumb_Preklici_1</t>
-  </si>
-  <si>
-    <t>C58038</t>
-  </si>
-  <si>
-    <t>WEB-Cezmejno_placilo-Gumb_Preklici_2</t>
-  </si>
-  <si>
-    <t>WEB-Cezmejno_placilo-Gumb_Preklici_3</t>
-  </si>
-  <si>
-    <t>WEB-Cezmejno_placilo-Gumb_nazaj_2</t>
-  </si>
-  <si>
-    <t>C58039</t>
-  </si>
-  <si>
-    <t>WEB-Osebni_racun-Transakcije-Potrdilo_o_transakciji</t>
-  </si>
-  <si>
-    <t>C59150</t>
-  </si>
-  <si>
-    <t>WEB-Varcevalni_racun-Transakcije-Potrdilo_o_transakciji</t>
-  </si>
-  <si>
-    <t>C59153</t>
-  </si>
-  <si>
-    <t>WEB-Varcevanje-Transakcije-Potrdilo_o_transakciji</t>
-  </si>
-  <si>
-    <t>C59154</t>
-  </si>
-  <si>
-    <t>WEB-Osebni_racun-Transakcije-Izvoz</t>
-  </si>
-  <si>
-    <t>C57032</t>
-  </si>
-  <si>
-    <t>WEB-Varcevanje-Izvoz</t>
-  </si>
-  <si>
-    <t>C57083</t>
-  </si>
-  <si>
-    <t>WEB-Osebni_racun-Transakcije-Filtri-Filtriranje_po_valuti</t>
-  </si>
-  <si>
-    <t>C57034</t>
-  </si>
-  <si>
-    <t>WEB-Osebni_racun-Transakcije-Filtri-Filtriranje_po_kategorijah</t>
-  </si>
-  <si>
-    <t>C57033</t>
-  </si>
-  <si>
-    <t>WEB-Varcevanje-Filtri-Filtriranje_po_tipu</t>
-  </si>
-  <si>
-    <t>C57088</t>
-  </si>
-  <si>
-    <t>PLA_WEB-eRacunu-Seznam_ponudnikov_eRacunov</t>
-  </si>
-  <si>
-    <t>C63490</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Ponudba-Predstavitvene_strani_produktov</t>
-  </si>
-  <si>
-    <t>C60786</t>
-  </si>
-  <si>
-    <t>PLA_WEB-PFM_Budgets_Add_new_budget_Delete_Edit</t>
-  </si>
-  <si>
-    <t>C59025,C59032,C59024</t>
-  </si>
-  <si>
-    <t>4,4,3</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Pretekla_placila-Seznam_placil</t>
-  </si>
-  <si>
-    <t>C57953</t>
-  </si>
-  <si>
-    <t>PLA-481_WEB_OsebnI_racun_Seznam_transakcij</t>
-  </si>
-  <si>
-    <t>C57840</t>
-  </si>
-  <si>
-    <t>PLA-506_WEB_Varcevanje_Seznam_transakcij</t>
-  </si>
-  <si>
-    <t>C57846</t>
-  </si>
-  <si>
-    <t>PLA_588_WEB_Varcevalni_racun_Osnovni_podatki_(glava)</t>
-  </si>
-  <si>
-    <t>C64697</t>
-  </si>
-  <si>
-    <t>PLA_587_WEB_Varcevalni_racun_Podrobnosti_Prikaz_podatkov</t>
-  </si>
-  <si>
-    <t>C57719</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Varcevanje-Podrobnosti</t>
-  </si>
-  <si>
-    <t>C57078</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Krediti-Osnovni_podatki(glava)</t>
-  </si>
-  <si>
-    <t>C57077</t>
-  </si>
-  <si>
-    <t>PLA_581_WEB-Produkti-Prikaz_produktov-Pooblascenski_racun</t>
-  </si>
-  <si>
-    <t>C57854,C57683</t>
-  </si>
-  <si>
-    <t>5,2</t>
-  </si>
-  <si>
-    <t>WEB-Produkti-Prikaz_produktov-Varcevanje</t>
-  </si>
-  <si>
-    <t>C57857</t>
-  </si>
-  <si>
-    <t>PLA-589_WEB-Produkti-Prikaz_produktov-Osnovni-racun</t>
-  </si>
-  <si>
-    <t>C57852</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Dokumenti-Prenos_dokumenta</t>
-  </si>
-  <si>
-    <t>C57969</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Session_Timeout-Izpis</t>
-  </si>
-  <si>
-    <t>C57726</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Namizje-Osvezitev_podatkov</t>
-  </si>
-  <si>
-    <t>C65780</t>
-  </si>
-  <si>
-    <t>PLA-503_WEB_Sporocanje_Novo_sporocilo_Vprasanje_s_priponko</t>
-  </si>
-  <si>
-    <t>C58075</t>
-  </si>
-  <si>
-    <t>PLA-501_WEB_Sporocanje_Inbox/Outbox</t>
-  </si>
-  <si>
-    <t>PLA-658_WEB_Sporocanje_Novo_sporocilo_Osebnemu_bancniku_s_priponko</t>
-  </si>
-  <si>
-    <t>C63350</t>
-  </si>
-  <si>
-    <t>WEB-Placila-Pregled</t>
-  </si>
-  <si>
-    <t>C61324</t>
-  </si>
-  <si>
-    <t>WEB-UPN-Gumb_nazaj_1</t>
-  </si>
-  <si>
-    <t>C57169</t>
-  </si>
-  <si>
-    <t>PLA-653_WEB_Sporocanje_Novo_sporocilo_Pritozba</t>
-  </si>
-  <si>
-    <t>C63345</t>
-  </si>
-  <si>
-    <t>PLA-654_WEB_Sporocanje_Novo_sporocilo_Osebnemu_bancniku</t>
-  </si>
-  <si>
-    <t>C63346</t>
-  </si>
-  <si>
-    <t>WEB-Sporocanje-Seznam_Podrobnosti_pritozb/ugovora_1</t>
-  </si>
-  <si>
-    <t>PLA-483_WEB_Varcevalni_racun_Seznam_transakcij</t>
-  </si>
-  <si>
-    <t>C57843</t>
-  </si>
-  <si>
-    <t>PLA_500_WEB_Dokumenti_Seznam_dokumentov</t>
-  </si>
-  <si>
-    <t>C57965</t>
-  </si>
-  <si>
-    <t>PLA-485_WEB_Cakajoca_placila_Seznam_placil</t>
-  </si>
-  <si>
-    <t>C57952</t>
-  </si>
-  <si>
-    <t>WEB-Vpis_in_registracija-Napacen_vpis_uporabnika</t>
-  </si>
-  <si>
-    <t>PLA_495_WEB_Placila_SEPA:Znotraj_Slovenije</t>
-  </si>
-  <si>
-    <t>C58152</t>
-  </si>
-  <si>
-    <t>PLA_494_WEB_Placila_SEPA:Znotraj_NLB</t>
-  </si>
-  <si>
-    <t>C57167,C60096</t>
-  </si>
-  <si>
-    <t>4,4</t>
-  </si>
-  <si>
-    <t>PLA-498_WEB_Placila_SEPA:V_prihodnje</t>
-  </si>
-  <si>
-    <t>C61597</t>
-  </si>
-  <si>
-    <t>WEB-Placila-Interni_prenos:OR-OR-TUJ#1</t>
-  </si>
-  <si>
-    <t>C59279</t>
-  </si>
-  <si>
-    <t>WEB-Placila-Interni_prenos:OR-OR-TUJ#1_Part_2</t>
-  </si>
-  <si>
-    <t>WEB-Placila-Interni_prenos:OR-OR-TUJ#3</t>
-  </si>
-  <si>
-    <t>C59927</t>
-  </si>
-  <si>
-    <t>WEB-Placila-Interni_prenos:OR-VAR-TUJ</t>
-  </si>
-  <si>
-    <t>C59934</t>
-  </si>
-  <si>
-    <t>PLA_634_WEB-Placila-SEPA:Humanitarna_organizacija_Part_2</t>
-  </si>
-  <si>
-    <t>C60097</t>
-  </si>
-  <si>
-    <t>PLA-650_WEB_Placila_Tuja_Izven_obmocja_EGP_TUJ_part_2</t>
-  </si>
-  <si>
-    <t>C59277</t>
-  </si>
-  <si>
-    <t>PLA-603_WEB_Pretekla_placila_Ponovi_interno_placilo_part_3</t>
-  </si>
-  <si>
-    <t>C62868</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Vpis_in_registracija-Vpis_uporabnika</t>
-  </si>
-  <si>
-    <t>C57170</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Kontakti-Ponovitev_placila_Part_2</t>
-  </si>
-  <si>
-    <t>C57611</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Kontakti-Ponovitev_placila_Part_1</t>
-  </si>
-  <si>
-    <t>PLA_584_WEB-Produkti-Prikaz_produktov-Depozit</t>
-  </si>
-  <si>
-    <t>C57855</t>
-  </si>
-  <si>
-    <t>PLA-602_WEB_Pretekla_placila_Ponovi_UPN_placilo_na_Fizicno_osebo_part_3</t>
-  </si>
-  <si>
-    <t>C65777</t>
-  </si>
-  <si>
-    <t>WEB-Pretekla_placila-Podatki_individualne_transakcije-SEPA_UPN_Part_2</t>
-  </si>
-  <si>
-    <t>C57109</t>
-  </si>
-  <si>
-    <t>PLA-491WEB_Placila_Interni_prenosOR-VR_EUR#1</t>
-  </si>
-  <si>
-    <t>C59929</t>
-  </si>
-  <si>
-    <t>WEB_Placila_Interni_prenosOR-VR_EUR#2</t>
-  </si>
-  <si>
-    <t>C59930</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Potrjevanje_placil-Ponovno_posiljanje_SMS</t>
-  </si>
-  <si>
-    <t>C57617,C63627</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Potrjevanje_placil-Napacen_vnos_OTP</t>
-  </si>
-  <si>
-    <t>C57619</t>
-  </si>
-  <si>
-    <t>PLA_508_WEB_Kontakti_Urejanje_Kontakta</t>
-  </si>
-  <si>
-    <t>C57613</t>
-  </si>
-  <si>
-    <t>PLA-489_WEB_Carovnik_za_placila_Izbira_prejemnika_iz_imenika</t>
-  </si>
-  <si>
-    <t>C57149</t>
-  </si>
-  <si>
-    <t>PLA_586_WEB_Osebni_racun_Podrobnosti</t>
-  </si>
-  <si>
-    <t>C57024</t>
-  </si>
-  <si>
-    <t>PLA-603_WEB_Pretekla_placila_Ponovi_interno_placilo</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Trajni_nalogi-Preklic_trajnega_naloga</t>
-  </si>
-  <si>
-    <t>C57127</t>
-  </si>
-  <si>
-    <t>PLA-605_WEB_Placilo_Nov_trajni_nalog_Do_preklica</t>
-  </si>
-  <si>
-    <t>C58153</t>
-  </si>
-  <si>
-    <t>5,5,3</t>
-  </si>
-  <si>
-    <t>PLA-490_WEB_Placila_Interni_prenos_OR-OR_EUR_Part_2</t>
-  </si>
-  <si>
-    <t>C59278</t>
-  </si>
-  <si>
-    <t>PLA-601_WEB_Pretekla_placila_Ponovi_UPN_placilo_na_Podjetje_part_3</t>
-  </si>
-  <si>
-    <t>C61673</t>
-  </si>
-  <si>
-    <t>PLA-507_WEB_Varcevanje_Podatki_individualne_transakcije</t>
-  </si>
-  <si>
-    <t>C57081</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_EUR-Pregled_placila(2.korak)</t>
-  </si>
-  <si>
-    <t>C57153</t>
-  </si>
-  <si>
-    <t>WEB-Interno_placilo_v_Tuji_valuti-Pregled_placila(2.korak)</t>
-  </si>
-  <si>
-    <t>C57159</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Potrjevanje_placil-Pregled_podatkov</t>
-  </si>
-  <si>
-    <t>C57615</t>
-  </si>
-  <si>
-    <t>WEB-Nov_trajni_nalog-Pregled_naloga(2.korak)</t>
-  </si>
-  <si>
-    <t>C57139</t>
-  </si>
-  <si>
-    <t>WEB-Produkti-Prikaz_produktov-Nastavitve-Skrij</t>
-  </si>
-  <si>
-    <t>C57681,C57682</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>WEB-Vstopna_stran-Menjava_jezika</t>
-  </si>
-  <si>
-    <t>C65669</t>
-  </si>
-  <si>
-    <t>PLA_497WEB-Placila-SEPA:Overdraft-NEGATIVEN</t>
-  </si>
-  <si>
-    <t>C61599</t>
-  </si>
-  <si>
-    <t>PLA-488_WEB_Menjava_valute_TUJ_EUR</t>
-  </si>
-  <si>
-    <t>C57145,C59280</t>
-  </si>
-  <si>
-    <t>4,3</t>
-  </si>
-  <si>
-    <t>PLA-484_WEB_Varcevalni_racun_Transakcije_Podatki_individualne_transakcije_1</t>
-  </si>
-  <si>
-    <t>C57043</t>
-  </si>
-  <si>
-    <t>PLA-484_WEB_Varcevalni_racun_Transakcije_Podatki_individualne_transakcije_1_Part_2</t>
-  </si>
-  <si>
-    <t>PLA_WEB-eRacuni-Narocanje</t>
-  </si>
-  <si>
-    <t>C57981</t>
-  </si>
-  <si>
-    <t>WEB-Cakajoca_placila-Podatki_individualne_transakcije-Interna_transakcija_Part_2</t>
-  </si>
-  <si>
-    <t>C57096</t>
-  </si>
-  <si>
-    <t>WEB-Cakajoca_placila-Podatki_individualne_transakcije-V_tujino_Part_2</t>
-  </si>
-  <si>
-    <t>C57097</t>
-  </si>
-  <si>
-    <t>WEB-Cakajoca_placila-Podatki_individualne_transakcije-Trajni_nalog_1_Part_2</t>
-  </si>
-  <si>
-    <t>C58127,C61317</t>
-  </si>
-  <si>
-    <t>WEB-Cakajoca_placila-Podatki_individualne_transakcije-Trajni_nalog_2_Part_2</t>
-  </si>
-  <si>
-    <t>WEB-Pretekla_placila-Podatki_individualne_transakcije-Interna_transakcija_Part_2</t>
-  </si>
-  <si>
-    <t>C57113</t>
-  </si>
-  <si>
-    <t>WEB-Pretekla_placila-Podatki_individualne_transakcije-V_tujino_Part_2</t>
-  </si>
-  <si>
-    <t>C57114</t>
-  </si>
-  <si>
-    <t>PLA-606_WEB_Placilo_Nov_trajni_nalog_Do_dolocenega_datuma</t>
-  </si>
-  <si>
-    <t>C59282</t>
-  </si>
-  <si>
-    <t>PLA-607_WEB_Placilo_Nov_trajni_nalog_Spremeni_posiljatelja_VR</t>
-  </si>
-  <si>
-    <t>C61616</t>
-  </si>
-  <si>
-    <t>WEB-Menjalnica-Menjava_Tuja/Tuja_valuta</t>
-  </si>
-  <si>
-    <t>C57144</t>
-  </si>
-  <si>
-    <t>PLA-601_WEB_Pretekla_placila_Ponovi_UPN_placilo_na_Podjetje_part_2</t>
-  </si>
-  <si>
-    <t>PLA-490_WEB_Placila_Interni_prenos_OR-OR_EUR</t>
-  </si>
-  <si>
-    <t>PLA-492WEB_Placila_Interni_prenos:OR-VAR_EUR</t>
-  </si>
-  <si>
-    <t>PLA-492WEB_Placila_Interni_prenos:OR-VAR_EUR_Part_2</t>
-  </si>
-  <si>
-    <t>PLA-493WEB-Placila-Interni_prenos:OR-KRD-EUR</t>
-  </si>
-  <si>
-    <t>C59935</t>
-  </si>
-  <si>
-    <t>PLA_494_WEB_Placila_SEPA:Znotraj_NLB_Part_2</t>
-  </si>
-  <si>
-    <t>C60096</t>
-  </si>
-  <si>
-    <t>PLA-496_WEB_Placila_SEPA_Izven_urnika</t>
-  </si>
-  <si>
-    <t>C59972</t>
-  </si>
-  <si>
-    <t>PLA-651_WEB_Placila_Tuja_Izven_obmocja_EGP_EUR</t>
-  </si>
-  <si>
-    <t>C58045,C62193</t>
-  </si>
-  <si>
-    <t>PLA-651_WEB_Placila_Tuja_Izven_obmocja_EGP_EUR_part_2</t>
-  </si>
-  <si>
-    <t>C62193</t>
-  </si>
-  <si>
-    <t>PLA-649_WEB_Placila_Tuja_Obmocje_EGP_part_2</t>
-  </si>
-  <si>
-    <t>C59276</t>
-  </si>
-  <si>
-    <t>PLA-415_CreatePayment_21_(Empty_Currency)</t>
-  </si>
-  <si>
-    <t>C57148</t>
-  </si>
-  <si>
-    <t>PLA-416_CreatePayment_22_(Unavailable_Currency_For_Account)</t>
-  </si>
-  <si>
-    <t>WEB-Pretekla_placila-Podatki_individualne_transakcije-SEPA_UPN_Part_1</t>
-  </si>
-  <si>
-    <t>WEB-UPN_Tuja-Osvezitev_stanj-Product_summary</t>
-  </si>
-  <si>
-    <t>C65829</t>
-  </si>
-  <si>
-    <t>WEB-UPN_Tuja-Osvezitev_stanj-Product_details</t>
-  </si>
-  <si>
-    <t>C65830</t>
-  </si>
-  <si>
-    <t>PLA-499_WEB_Kontakti_Nov_kontakt</t>
-  </si>
-  <si>
-    <t>C57607,C57618,C57616</t>
-  </si>
-  <si>
-    <t>5,4,4</t>
-  </si>
-  <si>
-    <t>PLA_WEB-eRacuni-Odjava</t>
-  </si>
-  <si>
-    <t>C57982</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Depozit-Osnovni_podatki(glava)</t>
-  </si>
-  <si>
-    <t>C57721</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Depozit-Podrobnosti</t>
-  </si>
-  <si>
-    <t>C57052</t>
-  </si>
-  <si>
-    <t>PLA_WEB-Krediti-Podrobnosti</t>
-  </si>
-  <si>
-    <t>C57722</t>
-  </si>
-  <si>
-    <t>PLA-605_WEB_Placilo_Nov_trajni_nalog_Do_preklica_part_2</t>
-  </si>
-  <si>
-    <t>PLA-650_WEB_Placila_Tuja_Izven_obmocja_EGP_TUJ_part_2_Upcoming_ver</t>
+    <t>C70880</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70898</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70899</t>
+  </si>
+  <si>
+    <t>Payments-Upcoming_Payments-Cancel_Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70897</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive-Payments_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70900</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Details-Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70773</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Back_Button_[WEB]</t>
+  </si>
+  <si>
+    <t>C70838</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Create_New_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70848</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_Modify_Data_[WEB]</t>
+  </si>
+  <si>
+    <t>C70845</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_In_Future_[WEB]</t>
+  </si>
+  <si>
+    <t>C70846</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70878</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Confirmation_[WEB]</t>
+  </si>
+  <si>
+    <t>C70879</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Accounts-Transactions-Filter_By_Type_[WEB]</t>
+  </si>
+  <si>
+    <t>C70785</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70803</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Accounts-Transactions_List_select_Currency_[WEB]</t>
+  </si>
+  <si>
+    <t>C70804</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_List_No_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>C70812</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
+  </si>
+  <si>
+    <t>C70814</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70865</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Flow_Disruption_Cancel-Back_[WEB]</t>
+  </si>
+  <si>
+    <t>C70849</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Current_Account</t>
+  </si>
+  <si>
+    <t>C70859</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70860</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive-Create_Confirmation_[WEB]</t>
+  </si>
+  <si>
+    <t>C70868</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70769</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70770</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Term_Deposits</t>
+  </si>
+  <si>
+    <t>C70778</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70881</t>
+  </si>
+  <si>
+    <t>Product_Summary-Term_Deposits_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70872</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Transactions_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70892</t>
+  </si>
+  <si>
+    <t>Savings_accounts-Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70895</t>
+  </si>
+  <si>
+    <t>Term_Deposits-Details_Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70821</t>
+  </si>
+  <si>
+    <t>Products_Current_Accounts-Cheques-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70800</t>
+  </si>
+  <si>
+    <t>Products_Current_Accounts-Cheques-Input_Fields-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70801</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Download_option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70784</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[WEB]</t>
+  </si>
+  <si>
+    <t>C70787</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Multiple-Filter_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70790</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70802</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70805</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Header-Display_[WEB]</t>
+  </si>
+  <si>
+    <t>C70774</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_List_No_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>C70807</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
+  </si>
+  <si>
+    <t>C70808</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70810</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Search_[WEB]</t>
+  </si>
+  <si>
+    <t>C70833</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70883</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70889</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70884</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70890</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70854</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Header_[WEB]</t>
+  </si>
+  <si>
+    <t>C70855</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan_[WEB]</t>
+  </si>
+  <si>
+    <t>C70863</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70864</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70876</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70866</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70877</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70856</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Current_Account</t>
+  </si>
+  <si>
+    <t>C70857</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[WEB]</t>
+  </si>
+  <si>
+    <t>C70862</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[WEB]</t>
+  </si>
+  <si>
+    <t>C70886</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70887</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70888</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Filter_Payments_By_Status_[WEB]</t>
+  </si>
+  <si>
+    <t>C70853</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70775</t>
+  </si>
+  <si>
+    <t>Product_Summary-Credit_Card_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70771</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Save_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70826</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Update_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70828</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Update_Recipient-Update_Account_number_[WEB]</t>
+  </si>
+  <si>
+    <t>C70835</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70885</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70891</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Account-Transactions-Filter_By_Type_[WEB]</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_Filter-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Product_Details_Financial_Details_Is_Not_Visible_[WEB]</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_Filter-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>Product_Summary_Favourite_account_[WEB]</t>
+  </si>
+  <si>
+    <t>Product_Summary_Sorting_on_the_Product_Summary_[WEB]</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Saving_Accounts</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Loan_Accounts</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Current_Foreign_Accounts</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Foreign_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Domestic_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>Product_Summary-Savings_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Details-Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>Term_Deposits-Accounts_Details[WEB]</t>
+  </si>
+  <si>
+    <t>Term_Deposits-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments-Upcoming_Payments-List_Of_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Delete_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3, </t>
+  </si>
+  <si>
+    <t>C70777</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -899,8 +558,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -914,24 +589,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -939,52 +606,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1000,15 +622,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1022,8 +636,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1042,6 +687,20 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1052,13 +711,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1070,115 +735,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1196,13 +753,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1214,13 +783,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1236,6 +871,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1246,11 +905,65 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1272,6 +985,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1280,82 +1002,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1364,134 +1014,275 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3043">
+  <cellXfs count="3175">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4538,52 +4329,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -4854,10 +4645,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="55.7142857142857" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" width="55.712962962963" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4881,23 +4672,383 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="3037">
-        <v>129</v>
-      </c>
-      <c r="B2" t="s" s="3038">
-        <v>130</v>
-      </c>
-      <c r="C2" t="s" s="3039">
+      <c r="A2" t="s" s="3061">
+        <v>147</v>
+      </c>
+      <c r="B2" t="s" s="3062">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s" s="3063">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s" s="3064">
         <v>8</v>
       </c>
-      <c r="D2" t="s" s="3040">
+      <c r="E2" t="s" s="3065">
         <v>9</v>
       </c>
-      <c r="E2" t="s" s="3041">
+      <c r="F2" t="s" s="3066">
         <v>10</v>
       </c>
-      <c r="F2" t="s" s="3042">
-        <v>11</v>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="3067">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s" s="3068">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="3069">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s" s="3070">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s" s="3071">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s" s="3072">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="3073">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s" s="3074">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s" s="3075">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="3076">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s" s="3077">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s" s="3078">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="3079">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s" s="3080">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s" s="3081">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s" s="3082">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s" s="3083">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s" s="3084">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="3085">
+        <v>91</v>
+      </c>
+      <c r="B6" t="s" s="3086">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s" s="3087">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s" s="3088">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s" s="3089">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s" s="3090">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="3091">
+        <v>148</v>
+      </c>
+      <c r="B7" t="s" s="3092">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s" s="3093">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s" s="3094">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s" s="3095">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s" s="3096">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="3097">
+        <v>149</v>
+      </c>
+      <c r="B8" t="s" s="3098">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s" s="3099">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s" s="3100">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s" s="3101">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s" s="3102">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="3103">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s" s="3104">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s" s="3105">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s" s="3106">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s" s="3107">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s" s="3108">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="3109">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s" s="3110">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s" s="3111">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s" s="3112">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s" s="3113">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s" s="3114">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="3115">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s" s="3116">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s" s="3117">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s" s="3118">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s" s="3119">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="3120">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="3121">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s" s="3122">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s" s="3123">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s" s="3124">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s" s="3125">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s" s="3126">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="3127">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="3128">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s" s="3129">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s" s="3130">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s" s="3131">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s" s="3132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="3133">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s" s="3134">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s" s="3135">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s" s="3136">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s" s="3137">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s" s="3138">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="3139">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s" s="3140">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s" s="3141">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s" s="3142">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s" s="3143">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s" s="3144">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="3145">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s" s="3146">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s" s="3147">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s" s="3148">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s" s="3149">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s" s="3150">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="3151">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s" s="3152">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s" s="3153">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s" s="3154">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s" s="3155">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s" s="3156">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="3157">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s" s="3158">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s" s="3159">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s" s="3160">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s" s="3161">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s" s="3162">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="3163">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s" s="3164">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s" s="3165">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s" s="3166">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s" s="3167">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s" s="3168">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="3169">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s" s="3170">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s" s="3171">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="3172">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s" s="3173">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s" s="3174">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
